--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128943349</v>
       </c>
       <c r="B5" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128943274</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128943349</v>
       </c>
       <c r="B5" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128943274</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128943349</v>
       </c>
       <c r="B5" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128943349</v>
       </c>
       <c r="B5" t="n">
-        <v>98586</v>
+        <v>98593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128943274</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128943349</v>
       </c>
       <c r="B5" t="n">
-        <v>98593</v>
+        <v>98595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128943349</v>
       </c>
       <c r="B5" t="n">
-        <v>98595</v>
+        <v>98621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128943349</v>
       </c>
       <c r="B5" t="n">
-        <v>98621</v>
+        <v>98622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128943349</v>
       </c>
       <c r="B5" t="n">
-        <v>98622</v>
+        <v>98623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128943274</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128943349</v>
       </c>
       <c r="B5" t="n">
-        <v>98623</v>
+        <v>98627</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>128943274</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128943349</v>
       </c>
       <c r="B5" t="n">
-        <v>98627</v>
+        <v>98629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128943349</v>
       </c>
       <c r="B5" t="n">
-        <v>98629</v>
+        <v>98633</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128943349</v>
       </c>
       <c r="B5" t="n">
-        <v>98633</v>
+        <v>98641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128943319</v>
+        <v>128943274</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334538</v>
+        <v>334587</v>
       </c>
       <c r="R2" t="n">
-        <v>6617241</v>
+        <v>6617191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -776,32 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128943296</v>
+        <v>128943332</v>
       </c>
       <c r="B3" t="n">
-        <v>5197</v>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334537</v>
+        <v>334695</v>
       </c>
       <c r="R3" t="n">
-        <v>6617241</v>
+        <v>6617202</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,17 +875,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris # Tallstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -892,32 +912,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128943274</v>
+        <v>128943319</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334587</v>
+        <v>334538</v>
       </c>
       <c r="R4" t="n">
-        <v>6617191</v>
+        <v>6617241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,21 +993,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1008,45 +1013,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128943349</v>
+        <v>128943298</v>
       </c>
       <c r="B5" t="n">
-        <v>98641</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Järnskogsfjället med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334539</v>
+        <v>334482</v>
       </c>
       <c r="R5" t="n">
-        <v>6617256</v>
+        <v>6617314</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,6 +1111,324 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128943296</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Järnskogsfjället med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>334537</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6617241</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128943349</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Järnskogsfjället med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>334539</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6617256</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128937206</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Järnskogsfjället, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>334686</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6617136</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Moa Berglund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Moa Berglund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 25800-2023 artfynd.xlsx
+++ b/artfynd/A 25800-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128943274</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128943332</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128943319</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128943298</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128943296</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128943349</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1433,8 +1468,22 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128937206</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>